--- a/data_u1/included_studies_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/included_studies_2025-08-15_LSR3_H.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC32EA9-3CAB-AB44-9EE4-278133C65F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C468BFD2-5DB0-8644-82C6-B2994469405B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5300" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22300" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of included studies" sheetId="9" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="313">
   <si>
     <t>ID</t>
   </si>
@@ -560,9 +560,6 @@
   </si>
   <si>
     <t>Men/women ≥55 years with Parkinson's disease psychosis (acute)</t>
-  </si>
-  <si>
-    <t>Efficacy, dropouts</t>
   </si>
   <si>
     <t>DB-RCT; single ascending dose (phase I)</t>
@@ -1443,7 +1440,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="29.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.1640625" customWidth="1"/>
     <col min="5" max="5" width="39" customWidth="1"/>
     <col min="6" max="6" width="33.1640625" customWidth="1"/>
@@ -1513,25 +1510,25 @@
         <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2" s="4">
         <v>164</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="L2">
         <v>2017</v>
@@ -1557,31 +1554,31 @@
         <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F3" t="s">
         <v>74</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H3" s="9">
         <v>131</v>
       </c>
       <c r="I3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L3">
         <v>2023</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>77</v>
@@ -1601,25 +1598,25 @@
         <v>69</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H4" s="4">
         <v>287</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="L4">
         <v>2022</v>
@@ -1689,25 +1686,25 @@
         <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H6" s="4">
         <v>64</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L6">
         <v>2019</v>
@@ -1733,19 +1730,19 @@
         <v>69</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="H7" s="4">
         <v>49</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>86</v>
@@ -1777,25 +1774,25 @@
         <v>88</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>89</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H8" s="11">
         <v>1030</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L8" t="s">
         <v>86</v>
@@ -1821,19 +1818,19 @@
         <v>88</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H9" s="4">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>86</v>
@@ -1909,25 +1906,25 @@
         <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F11" t="s">
         <v>99</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H11">
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L11">
         <v>2020</v>
@@ -1953,31 +1950,31 @@
         <v>88</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H12" s="11">
         <v>83</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L12" s="9">
         <v>2023</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N12" t="s">
         <v>72</v>
@@ -2041,19 +2038,19 @@
         <v>88</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H14" s="4">
         <v>52</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>86</v>
@@ -2085,19 +2082,19 @@
         <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F15" t="s">
         <v>110</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>86</v>
@@ -2129,25 +2126,25 @@
         <v>88</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="H16" s="4">
         <v>105</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L16">
         <v>2015</v>
@@ -2156,7 +2153,7 @@
         <v>2</v>
       </c>
       <c r="N16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2173,25 +2170,25 @@
         <v>88</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>114</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H17" s="4">
         <v>48</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J17" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="L17">
         <v>2014</v>
@@ -2217,25 +2214,25 @@
         <v>88</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>116</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H18" s="4">
         <v>48</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="L18">
         <v>2014</v>
@@ -2261,25 +2258,25 @@
         <v>88</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>118</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H19" s="4">
         <v>18</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="L19">
         <v>2015</v>
@@ -2305,25 +2302,25 @@
         <v>88</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H20" s="4">
         <v>68</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L20">
         <v>2020</v>
@@ -2393,25 +2390,25 @@
         <v>88</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H22" s="4">
         <v>60</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L22" s="14">
         <v>2024</v>
@@ -2437,25 +2434,25 @@
         <v>88</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H23" s="16">
         <v>19</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L23" s="14">
         <v>2024</v>
@@ -2525,25 +2522,25 @@
         <v>88</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F25" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>284</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>285</v>
       </c>
       <c r="H25" s="11">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L25" s="9">
         <v>2023</v>
@@ -2552,7 +2549,7 @@
         <v>2</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2569,25 +2566,25 @@
         <v>88</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>135</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H26" s="4">
         <v>245</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L26">
         <v>2018</v>
@@ -2657,25 +2654,25 @@
         <v>88</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>173</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H28" s="4">
         <v>39</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="L28">
         <v>2023</v>
@@ -2701,25 +2698,25 @@
         <v>88</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>144</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H29" s="4">
         <v>464</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="L29" t="s">
         <v>86</v>
@@ -2745,25 +2742,25 @@
         <v>88</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H30" s="4">
         <v>463</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L30">
         <v>2023</v>
@@ -2772,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2789,25 +2786,25 @@
         <v>88</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H31" s="4">
         <v>462</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L31">
         <v>2023</v>
@@ -2816,7 +2813,7 @@
         <v>2</v>
       </c>
       <c r="N31" t="s">
-        <v>174</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -2845,19 +2842,19 @@
         <v>463</v>
       </c>
       <c r="I32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J32" t="s">
         <v>150</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L32" s="14">
         <v>2023</v>
       </c>
       <c r="M32" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N32" t="s">
         <v>72</v>
@@ -2877,25 +2874,25 @@
         <v>88</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H33" s="11">
         <v>302</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="L33">
         <v>2022</v>
@@ -2933,13 +2930,13 @@
         <v>101</v>
       </c>
       <c r="I34" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J34" t="s">
         <v>153</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L34" s="14">
         <v>2024</v>
@@ -2977,7 +2974,7 @@
         <v>67</v>
       </c>
       <c r="I35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J35" t="s">
         <v>156</v>
@@ -2997,37 +2994,37 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B36" t="s">
         <v>166</v>
       </c>
       <c r="C36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D36" t="s">
         <v>88</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>275</v>
-      </c>
       <c r="G36" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H36" s="8">
         <v>22</v>
       </c>
       <c r="I36" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="L36">
         <v>2023</v>
@@ -3036,42 +3033,42 @@
         <v>2</v>
       </c>
       <c r="N36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C37" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D37" t="s">
         <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F37" t="s">
         <v>99</v>
       </c>
       <c r="G37" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H37">
         <v>35</v>
       </c>
       <c r="I37" t="s">
+        <v>308</v>
+      </c>
+      <c r="J37" t="s">
         <v>309</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>310</v>
-      </c>
-      <c r="K37" t="s">
-        <v>311</v>
       </c>
       <c r="L37">
         <v>2019</v>
@@ -3085,37 +3082,37 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C38" t="s">
+        <v>304</v>
+      </c>
+      <c r="D38" t="s">
         <v>305</v>
       </c>
-      <c r="D38" t="s">
-        <v>306</v>
-      </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H38">
         <v>522</v>
       </c>
       <c r="I38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J38" t="s">
+        <v>311</v>
+      </c>
+      <c r="K38" t="s">
         <v>312</v>
-      </c>
-      <c r="K38" t="s">
-        <v>313</v>
       </c>
       <c r="M38" t="s">
         <v>31</v>
@@ -3152,6 +3149,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9667EA7A926CE44956D0B5DCD9CC853" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d16da6adbc1ddf8797d77451e3cf87a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d306db0-a384-4295-b85c-939a3142a74b" xmlns:ns3="a3c2bd72-a5a7-4afd-b193-b6de680f91cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b95c06a4b98ee3d310726f4e0c3474a8" ns2:_="" ns3:_="">
     <xsd:import namespace="1d306db0-a384-4295-b85c-939a3142a74b"/>
@@ -3334,22 +3346,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3430553F-8EDA-442D-BB5A-06A762556CDB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB39C5E6-EEF6-4ED3-A020-8D524EF8560D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E7D91A3-6CE8-4434-B49C-80EABACC49BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3366,21 +3380,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB39C5E6-EEF6-4ED3-A020-8D524EF8560D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3430553F-8EDA-442D-BB5A-06A762556CDB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data_u1/included_studies_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/included_studies_2025-08-15_LSR3_H.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C468BFD2-5DB0-8644-82C6-B2994469405B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215C4B0F-335F-3941-A2A8-E3B805E54EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22300" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of included studies" sheetId="9" r:id="rId1"/>
@@ -244,9 +244,6 @@
     <t>Available data</t>
   </si>
   <si>
-    <t>BP30134, NCT02699372</t>
-  </si>
-  <si>
     <t>Hoffmann-La Roche</t>
   </si>
   <si>
@@ -977,6 +974,9 @@
   </si>
   <si>
     <t>August 31 2028</t>
+  </si>
+  <si>
+    <t>BP30134, NCT02699372, 2015-005509-35</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1443,7 @@
     <col min="3" max="3" width="29.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.1640625" customWidth="1"/>
     <col min="5" max="5" width="39" customWidth="1"/>
-    <col min="6" max="6" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="90.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
     <col min="8" max="8" width="17.1640625" customWidth="1"/>
     <col min="9" max="9" width="18.6640625" customWidth="1"/>
@@ -1487,7 +1487,7 @@
         <v>65</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>66</v>
@@ -1504,31 +1504,31 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" t="s">
         <v>68</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="H2" s="4">
         <v>164</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="L2">
         <v>2017</v>
@@ -1537,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="170" x14ac:dyDescent="0.2">
@@ -1545,43 +1545,43 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" t="s">
         <v>73</v>
       </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F3" t="s">
-        <v>74</v>
-      </c>
       <c r="G3" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H3" s="9">
         <v>131</v>
       </c>
       <c r="I3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L3">
         <v>2023</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1589,34 +1589,34 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H4" s="4">
         <v>287</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="L4">
         <v>2022</v>
@@ -1625,7 +1625,7 @@
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
@@ -1633,34 +1633,34 @@
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" t="s">
         <v>78</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>79</v>
-      </c>
-      <c r="G5" t="s">
-        <v>80</v>
       </c>
       <c r="H5">
         <v>20</v>
       </c>
       <c r="I5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" t="s">
         <v>81</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>82</v>
-      </c>
-      <c r="K5" t="s">
-        <v>83</v>
       </c>
       <c r="L5">
         <v>2022</v>
@@ -1669,7 +1669,7 @@
         <v>2</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1680,31 +1680,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="H6" s="4">
         <v>64</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L6">
         <v>2019</v>
@@ -1713,7 +1713,7 @@
         <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1721,34 +1721,34 @@
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="H7" s="4">
         <v>49</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L7">
         <v>2015</v>
@@ -1757,7 +1757,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1768,75 +1768,75 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
         <v>87</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="H8" s="11">
         <v>1030</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M8" t="s">
         <v>31</v>
       </c>
       <c r="N8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="H9" s="4">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L9">
         <v>2021</v>
@@ -1845,42 +1845,42 @@
         <v>2</v>
       </c>
       <c r="N9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" t="s">
         <v>93</v>
       </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>94</v>
-      </c>
-      <c r="G10" t="s">
-        <v>95</v>
       </c>
       <c r="H10">
         <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J10" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" t="s">
         <v>96</v>
-      </c>
-      <c r="K10" t="s">
-        <v>97</v>
       </c>
       <c r="L10">
         <v>2018</v>
@@ -1889,7 +1889,7 @@
         <v>2</v>
       </c>
       <c r="N10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="102" x14ac:dyDescent="0.2">
@@ -1900,31 +1900,31 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" t="s">
         <v>98</v>
       </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>202</v>
-      </c>
-      <c r="F11" t="s">
-        <v>99</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H11">
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L11">
         <v>2020</v>
@@ -1933,7 +1933,7 @@
         <v>2</v>
       </c>
       <c r="N11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1944,40 +1944,40 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H12" s="11">
         <v>83</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L12" s="9">
         <v>2023</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
@@ -1985,78 +1985,78 @@
         <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" t="s">
         <v>102</v>
       </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>103</v>
-      </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H13">
         <v>220</v>
       </c>
       <c r="I13" t="s">
+        <v>103</v>
+      </c>
+      <c r="J13" t="s">
         <v>104</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>105</v>
       </c>
-      <c r="K13" t="s">
-        <v>106</v>
-      </c>
       <c r="L13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s">
         <v>31</v>
       </c>
       <c r="N13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
         <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="H14" s="4">
         <v>52</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L14">
         <v>2021</v>
@@ -2065,7 +2065,7 @@
         <v>2</v>
       </c>
       <c r="N14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
@@ -2076,31 +2076,31 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F15" t="s">
         <v>109</v>
       </c>
-      <c r="D15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" t="s">
-        <v>190</v>
-      </c>
-      <c r="F15" t="s">
-        <v>110</v>
-      </c>
       <c r="G15" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L15">
         <v>2021</v>
@@ -2109,7 +2109,7 @@
         <v>2</v>
       </c>
       <c r="N15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2120,31 +2120,31 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="H16" s="4">
         <v>105</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L16">
         <v>2015</v>
@@ -2153,7 +2153,7 @@
         <v>2</v>
       </c>
       <c r="N16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2164,31 +2164,31 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="H17" s="4">
         <v>48</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J17" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="L17">
         <v>2014</v>
@@ -2197,7 +2197,7 @@
         <v>2</v>
       </c>
       <c r="N17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2208,31 +2208,31 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="H18" s="4">
         <v>48</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="L18">
         <v>2014</v>
@@ -2241,7 +2241,7 @@
         <v>2</v>
       </c>
       <c r="N18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2252,31 +2252,31 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="H19" s="4">
         <v>18</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="L19">
         <v>2015</v>
@@ -2285,7 +2285,7 @@
         <v>2</v>
       </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2296,31 +2296,31 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="H20" s="4">
         <v>68</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L20">
         <v>2020</v>
@@ -2329,7 +2329,7 @@
         <v>2</v>
       </c>
       <c r="N20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
@@ -2337,34 +2337,34 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
         <v>120</v>
       </c>
-      <c r="D21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>121</v>
       </c>
-      <c r="F21" t="s">
-        <v>122</v>
-      </c>
       <c r="G21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H21">
         <v>22</v>
       </c>
       <c r="I21" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" t="s">
         <v>123</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>124</v>
-      </c>
-      <c r="K21" t="s">
-        <v>125</v>
       </c>
       <c r="L21">
         <v>2023</v>
@@ -2373,7 +2373,7 @@
         <v>2</v>
       </c>
       <c r="N21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2384,31 +2384,31 @@
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="H22" s="4">
         <v>60</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L22" s="14">
         <v>2024</v>
@@ -2417,7 +2417,7 @@
         <v>2</v>
       </c>
       <c r="N22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2428,31 +2428,31 @@
         <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H23" s="16">
         <v>19</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L23" s="14">
         <v>2024</v>
@@ -2461,7 +2461,7 @@
         <v>2</v>
       </c>
       <c r="N23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
@@ -2469,43 +2469,43 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" t="s">
         <v>128</v>
-      </c>
-      <c r="D24" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" t="s">
-        <v>99</v>
-      </c>
-      <c r="G24" t="s">
-        <v>129</v>
       </c>
       <c r="H24">
         <v>24</v>
       </c>
       <c r="I24" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" t="s">
         <v>130</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>131</v>
       </c>
-      <c r="K24" t="s">
-        <v>132</v>
-      </c>
       <c r="L24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M24" t="s">
         <v>31</v>
       </c>
       <c r="N24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2513,34 +2513,34 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F25" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="H25" s="11">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L25" s="9">
         <v>2023</v>
@@ -2549,7 +2549,7 @@
         <v>2</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2560,31 +2560,31 @@
         <v>15</v>
       </c>
       <c r="C26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="G26" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H26" s="4">
         <v>245</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L26">
         <v>2018</v>
@@ -2593,7 +2593,7 @@
         <v>2</v>
       </c>
       <c r="N26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
@@ -2604,31 +2604,31 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" t="s">
         <v>136</v>
       </c>
-      <c r="D27" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>137</v>
       </c>
-      <c r="F27" t="s">
-        <v>138</v>
-      </c>
       <c r="G27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H27">
         <v>157</v>
       </c>
       <c r="I27" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" t="s">
         <v>139</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>140</v>
-      </c>
-      <c r="K27" t="s">
-        <v>141</v>
       </c>
       <c r="L27">
         <v>2019</v>
@@ -2637,7 +2637,7 @@
         <v>2</v>
       </c>
       <c r="N27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2648,31 +2648,31 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="H28" s="4">
         <v>39</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="L28">
         <v>2023</v>
@@ -2681,7 +2681,7 @@
         <v>2</v>
       </c>
       <c r="N28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2692,40 +2692,40 @@
         <v>38</v>
       </c>
       <c r="C29" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="H29" s="4">
         <v>464</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="L29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M29" t="s">
         <v>31</v>
       </c>
       <c r="N29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2736,31 +2736,31 @@
         <v>22</v>
       </c>
       <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D30" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="H30" s="4">
         <v>463</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L30">
         <v>2023</v>
@@ -2769,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="N30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2780,31 +2780,31 @@
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H31" s="4">
         <v>462</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L31">
         <v>2023</v>
@@ -2813,7 +2813,7 @@
         <v>2</v>
       </c>
       <c r="N31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -2821,43 +2821,43 @@
         <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" t="s">
         <v>148</v>
       </c>
-      <c r="D32" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" t="s">
-        <v>149</v>
-      </c>
       <c r="F32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H32" s="14">
         <v>463</v>
       </c>
       <c r="I32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L32" s="14">
         <v>2023</v>
       </c>
       <c r="M32" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2865,34 +2865,34 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="H33" s="11">
         <v>302</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="L33">
         <v>2022</v>
@@ -2901,7 +2901,7 @@
         <v>2</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2909,34 +2909,34 @@
         <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H34" s="14">
         <v>101</v>
       </c>
       <c r="I34" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L34" s="14">
         <v>2024</v>
@@ -2945,7 +2945,7 @@
         <v>2</v>
       </c>
       <c r="N34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2953,78 +2953,78 @@
         <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" t="s">
         <v>154</v>
       </c>
-      <c r="D35" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" t="s">
-        <v>155</v>
-      </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H35">
         <v>67</v>
       </c>
       <c r="I35" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J35" t="s">
+        <v>155</v>
+      </c>
+      <c r="K35" t="s">
         <v>156</v>
       </c>
-      <c r="K35" t="s">
-        <v>157</v>
-      </c>
       <c r="L35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M35" t="s">
         <v>31</v>
       </c>
       <c r="N35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>274</v>
+      </c>
+      <c r="B36" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" t="s">
+        <v>271</v>
+      </c>
+      <c r="D36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G36" s="7" t="s">
         <v>275</v>
-      </c>
-      <c r="B36" t="s">
-        <v>166</v>
-      </c>
-      <c r="C36" t="s">
-        <v>272</v>
-      </c>
-      <c r="D36" t="s">
-        <v>88</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>276</v>
       </c>
       <c r="H36" s="8">
         <v>22</v>
       </c>
       <c r="I36" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="L36">
         <v>2023</v>
@@ -3033,42 +3033,42 @@
         <v>2</v>
       </c>
       <c r="N36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C37" t="s">
+        <v>301</v>
+      </c>
+      <c r="D37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" t="s">
         <v>302</v>
       </c>
-      <c r="D37" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" t="s">
-        <v>303</v>
-      </c>
       <c r="F37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H37">
         <v>35</v>
       </c>
       <c r="I37" t="s">
+        <v>307</v>
+      </c>
+      <c r="J37" t="s">
         <v>308</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>309</v>
-      </c>
-      <c r="K37" t="s">
-        <v>310</v>
       </c>
       <c r="L37">
         <v>2019</v>
@@ -3077,48 +3077,48 @@
         <v>2</v>
       </c>
       <c r="N37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C38" t="s">
+        <v>303</v>
+      </c>
+      <c r="D38" t="s">
         <v>304</v>
       </c>
-      <c r="D38" t="s">
-        <v>305</v>
-      </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G38" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H38">
         <v>522</v>
       </c>
       <c r="I38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J38" t="s">
+        <v>310</v>
+      </c>
+      <c r="K38" t="s">
         <v>311</v>
-      </c>
-      <c r="K38" t="s">
-        <v>312</v>
       </c>
       <c r="M38" t="s">
         <v>31</v>
       </c>
       <c r="N38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3155,15 +3155,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9667EA7A926CE44956D0B5DCD9CC853" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d16da6adbc1ddf8797d77451e3cf87a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d306db0-a384-4295-b85c-939a3142a74b" xmlns:ns3="a3c2bd72-a5a7-4afd-b193-b6de680f91cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b95c06a4b98ee3d310726f4e0c3474a8" ns2:_="" ns3:_="">
     <xsd:import namespace="1d306db0-a384-4295-b85c-939a3142a74b"/>
@@ -3346,6 +3337,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3430553F-8EDA-442D-BB5A-06A762556CDB}">
   <ds:schemaRefs>
@@ -3356,14 +3356,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB39C5E6-EEF6-4ED3-A020-8D524EF8560D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E7D91A3-6CE8-4434-B49C-80EABACC49BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3380,4 +3372,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB39C5E6-EEF6-4ED3-A020-8D524EF8560D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data_u1/included_studies_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/included_studies_2025-08-15_LSR3_H.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215C4B0F-335F-3941-A2A8-E3B805E54EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FE7FC1-1323-624A-B876-F3467FB8825B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5600" yWindow="1240" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of included studies" sheetId="9" r:id="rId1"/>
@@ -2795,7 +2795,7 @@
         <v>208</v>
       </c>
       <c r="H31" s="4">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>217</v>
@@ -3149,12 +3149,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9667EA7A926CE44956D0B5DCD9CC853" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d16da6adbc1ddf8797d77451e3cf87a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d306db0-a384-4295-b85c-939a3142a74b" xmlns:ns3="a3c2bd72-a5a7-4afd-b193-b6de680f91cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b95c06a4b98ee3d310726f4e0c3474a8" ns2:_="" ns3:_="">
     <xsd:import namespace="1d306db0-a384-4295-b85c-939a3142a74b"/>
@@ -3337,6 +3331,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3347,15 +3347,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3430553F-8EDA-442D-BB5A-06A762556CDB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E7D91A3-6CE8-4434-B49C-80EABACC49BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3374,6 +3365,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3430553F-8EDA-442D-BB5A-06A762556CDB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB39C5E6-EEF6-4ED3-A020-8D524EF8560D}">
   <ds:schemaRefs>
